--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484658_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484658_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.8076</v>
+        <v>6.1129</v>
       </c>
       <c r="E2" t="n">
-        <v>2.7337</v>
+        <v>2.94</v>
       </c>
       <c r="F2" t="n">
-        <v>3.0739</v>
+        <v>3.173</v>
       </c>
       <c r="G2" t="n">
         <v>7.6646</v>
@@ -610,13 +610,13 @@
         <v>2.5656</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.5742</v>
+        <v>-0.2689</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4789</v>
+        <v>-0.2726</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0954</v>
+        <v>0.0037</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.094</v>
+        <v>4.7472</v>
       </c>
       <c r="E3" t="n">
         <v>3.9405</v>
       </c>
       <c r="F3" t="n">
-        <v>1.1536</v>
+        <v>0.8068</v>
       </c>
       <c r="G3" t="n">
         <v>3.47</v>
@@ -688,13 +688,13 @@
         <v>0.5498</v>
       </c>
       <c r="S3" t="n">
-        <v>1.3283</v>
+        <v>0.9815</v>
       </c>
       <c r="T3" t="n">
         <v>0.5121</v>
       </c>
       <c r="U3" t="n">
-        <v>0.8163</v>
+        <v>0.4694</v>
       </c>
       <c r="V3" t="n">
         <v>1.5785</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.3127</v>
+        <v>2.7934</v>
       </c>
       <c r="E4" t="n">
-        <v>1.4072</v>
+        <v>1.0365</v>
       </c>
       <c r="F4" t="n">
-        <v>1.9055</v>
+        <v>1.7569</v>
       </c>
       <c r="G4" t="n">
         <v>2.0552</v>
@@ -766,13 +766,13 @@
         <v>2.1991</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4695</v>
+        <v>-0.0498</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3824</v>
+        <v>0.0117</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0871</v>
+        <v>-0.0615</v>
       </c>
       <c r="V4" t="n">
         <v>-0.3115</v>
@@ -799,10 +799,10 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2326</v>
+        <v>2.4389</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.2761</v>
+        <v>-0.0698</v>
       </c>
       <c r="F5" t="n">
         <v>2.5087</v>
@@ -844,10 +844,10 @@
         <v>1.6493</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.3552</v>
+        <v>-1.149</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.9909</v>
+        <v>-0.7847</v>
       </c>
       <c r="U5" t="n">
         <v>-0.3643</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.7502</v>
+        <v>1.775</v>
       </c>
       <c r="E6" t="n">
         <v>1.3345</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4157</v>
+        <v>0.4404</v>
       </c>
       <c r="G6" t="n">
         <v>1.202</v>
@@ -922,13 +922,13 @@
         <v>0.9163</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.6796</v>
+        <v>-0.6548</v>
       </c>
       <c r="T6" t="n">
         <v>-0.1652</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5144</v>
+        <v>-0.4896</v>
       </c>
       <c r="V6" t="n">
         <v>0.3115</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.4947</v>
+        <v>1.5556</v>
       </c>
       <c r="E7" t="n">
-        <v>2.4544</v>
+        <v>2.3172</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.9597</v>
+        <v>-0.7616000000000001</v>
       </c>
       <c r="G7" t="n">
         <v>2.0901</v>
@@ -1000,13 +1000,13 @@
         <v>1.0995</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4176</v>
+        <v>-0.3567</v>
       </c>
       <c r="T7" t="n">
-        <v>0.402</v>
+        <v>0.2647</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.8196</v>
+        <v>-0.6214</v>
       </c>
       <c r="V7" t="n">
         <v>-1.2774</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.3427</v>
+        <v>1.4747</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.9458</v>
+        <v>-1.7396</v>
       </c>
       <c r="F8" t="n">
-        <v>3.2886</v>
+        <v>3.2142</v>
       </c>
       <c r="G8" t="n">
         <v>1.891</v>
@@ -1078,13 +1078,13 @@
         <v>2.9321</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5978</v>
+        <v>-0.4659</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4789</v>
+        <v>-0.2726</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.119</v>
+        <v>-0.1933</v>
       </c>
       <c r="V8" t="n">
         <v>0.9658</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4074</v>
+        <v>0.7454</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.419</v>
+        <v>-1.1305</v>
       </c>
       <c r="F10" t="n">
-        <v>1.8264</v>
+        <v>1.8759</v>
       </c>
       <c r="G10" t="n">
         <v>-0.1761</v>
@@ -1234,13 +1234,13 @@
         <v>0.5498</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0338</v>
+        <v>0.3718</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3303</v>
+        <v>-0.0418</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3641</v>
+        <v>0.4136</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.3595</v>
+        <v>-0.1643</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.5988</v>
+        <v>-2.5027</v>
       </c>
       <c r="F11" t="n">
-        <v>2.2393</v>
+        <v>2.3384</v>
       </c>
       <c r="G11" t="n">
         <v>1.7282</v>
@@ -1312,13 +1312,13 @@
         <v>0.9163</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8495</v>
+        <v>-0.6542</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2753</v>
+        <v>-0.1791</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5742</v>
+        <v>-0.4751</v>
       </c>
       <c r="V11" t="n">
         <v>-0.3219</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.8968</v>
+        <v>-3.7427</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.1744</v>
+        <v>-4.1193</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2775</v>
+        <v>0.3766</v>
       </c>
       <c r="G12" t="n">
         <v>-2.4312</v>
@@ -1390,13 +1390,13 @@
         <v>1.2828</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.0154</v>
+        <v>-0.8612</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6056</v>
+        <v>-0.5505</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4098</v>
+        <v>-0.3107</v>
       </c>
       <c r="V12" t="n">
         <v>-0.6335</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>18.1358</v>
+        <v>18.6863</v>
       </c>
       <c r="E13" t="n">
-        <v>2.406399999999998</v>
+        <v>2.957000000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>15.7295</v>
+        <v>15.7293</v>
       </c>
       <c r="G13" t="n">
         <v>20.2151</v>
@@ -1468,10 +1468,10 @@
         <v>14.6606</v>
       </c>
       <c r="S13" t="n">
-        <v>-3.6577</v>
+        <v>-3.1072</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.0286</v>
+        <v>-1.478</v>
       </c>
       <c r="U13" t="n">
         <v>-1.6292</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.0055</v>
+        <v>3.2191</v>
       </c>
       <c r="E14" t="n">
-        <v>1.6018</v>
+        <v>2.5633</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4037</v>
+        <v>0.6558</v>
       </c>
       <c r="G14" t="n">
         <v>1.8136</v>
@@ -1546,13 +1546,13 @@
         <v>2.1991</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.0909</v>
+        <v>0.1227</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.0098</v>
+        <v>-0.0482</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.08110000000000001</v>
+        <v>0.171</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.694</v>
+        <v>0.0486</v>
       </c>
       <c r="E16" t="n">
-        <v>0.7713</v>
+        <v>0.0021</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.07729999999999999</v>
+        <v>0.0466</v>
       </c>
       <c r="G16" t="n">
         <v>-1.8788</v>
@@ -1702,13 +1702,13 @@
         <v>1.0995</v>
       </c>
       <c r="S16" t="n">
-        <v>1.6565</v>
+        <v>1.0111</v>
       </c>
       <c r="T16" t="n">
-        <v>1.5739</v>
+        <v>0.8047</v>
       </c>
       <c r="U16" t="n">
-        <v>0.08260000000000001</v>
+        <v>0.2064</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>E. DIAGNE</t>
+          <t>M. PERAL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,58 +1735,58 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.4972</v>
+        <v>-0.1989</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8566</v>
+        <v>-0.09</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.3538</v>
+        <v>-0.1089</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.4644</v>
+        <v>-0.4129</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.1469</v>
+        <v>-1.5477</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.3175</v>
+        <v>1.1348</v>
       </c>
       <c r="J17" t="n">
-        <v>1.2254</v>
+        <v>-0.0892</v>
       </c>
       <c r="K17" t="n">
-        <v>0.5169</v>
+        <v>-0.8394</v>
       </c>
       <c r="L17" t="n">
-        <v>0.7085</v>
+        <v>0.7501</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.6898</v>
+        <v>-0.3237</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.6638</v>
+        <v>-0.7083</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.0259</v>
+        <v>0.3846</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>0.1833</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.0995</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.0995</v>
+        <v>0.1833</v>
       </c>
       <c r="S17" t="n">
-        <v>1.2891</v>
+        <v>0.3528</v>
       </c>
       <c r="T17" t="n">
-        <v>0.7308</v>
+        <v>-0.0007</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5584</v>
+        <v>0.3535</v>
       </c>
       <c r="V17" t="n">
         <v>-0.3219</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. PERAL</t>
+          <t>E. DIAGNE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.8064</v>
+        <v>-0.9488</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.4746</v>
+        <v>0.3759</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.3318</v>
+        <v>-1.3247</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.4129</v>
+        <v>-1.4644</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.5477</v>
+        <v>-1.1469</v>
       </c>
       <c r="I18" t="n">
-        <v>1.1348</v>
+        <v>-0.3175</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.0892</v>
+        <v>1.2254</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.8394</v>
+        <v>0.5169</v>
       </c>
       <c r="L18" t="n">
-        <v>0.7501</v>
+        <v>0.7085</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.3237</v>
+        <v>-2.6898</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.7083</v>
+        <v>-1.6638</v>
       </c>
       <c r="O18" t="n">
-        <v>0.3846</v>
+        <v>-1.0259</v>
       </c>
       <c r="P18" t="n">
-        <v>0.1833</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.0995</v>
       </c>
       <c r="R18" t="n">
-        <v>0.1833</v>
+        <v>1.0995</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2548</v>
+        <v>0.8375</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3854</v>
+        <v>0.25</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1305</v>
+        <v>0.5875</v>
       </c>
       <c r="V18" t="n">
         <v>-0.3219</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.1217</v>
+        <v>-1.7731</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.6982</v>
+        <v>-1.9866</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5765</v>
+        <v>0.2136</v>
       </c>
       <c r="G19" t="n">
         <v>-1.8196</v>
@@ -1936,13 +1936,13 @@
         <v>1.8326</v>
       </c>
       <c r="S19" t="n">
-        <v>1.4755</v>
+        <v>0.8241000000000001</v>
       </c>
       <c r="T19" t="n">
-        <v>0.5286999999999999</v>
+        <v>0.2402</v>
       </c>
       <c r="U19" t="n">
-        <v>0.9468</v>
+        <v>0.5839</v>
       </c>
       <c r="V19" t="n">
         <v>0.3219</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. NEBOT GARCIA</t>
+          <t>A. ALBA GONZALEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.3317</v>
+        <v>-2.1957</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.4319</v>
+        <v>-2.6759</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1002</v>
+        <v>0.4803</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.9484</v>
+        <v>-2.4766</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.0605</v>
+        <v>-0.5856</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.8879</v>
+        <v>-1.891</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.5224</v>
+        <v>-1.8856</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.9231</v>
+        <v>0.486</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.5994</v>
+        <v>-2.3717</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.4259</v>
+        <v>-0.591</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.1374</v>
+        <v>-1.0716</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.2885</v>
+        <v>0.4807</v>
       </c>
       <c r="P20" t="n">
-        <v>0.733</v>
+        <v>0.9163</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R20" t="n">
-        <v>0.733</v>
+        <v>1.8326</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1164</v>
+        <v>0.6316000000000001</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0905</v>
+        <v>0.126</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2069</v>
+        <v>0.5056</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-1.267</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>C. WHITSON</t>
+          <t>M. NEBOT GARCIA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.4528</v>
+        <v>-2.5458</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.3109</v>
+        <v>-2.7204</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.1419</v>
+        <v>0.1745</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.7354000000000001</v>
+        <v>-2.9484</v>
       </c>
       <c r="H21" t="n">
-        <v>0.6138</v>
+        <v>-2.0605</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.3492</v>
+        <v>-0.8879</v>
       </c>
       <c r="J21" t="n">
-        <v>0.5609</v>
+        <v>-2.5224</v>
       </c>
       <c r="K21" t="n">
-        <v>1.5573</v>
+        <v>-1.9231</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.9964</v>
+        <v>-0.5994</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.2962</v>
+        <v>-0.4259</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.9434</v>
+        <v>-0.1374</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.3528</v>
+        <v>-0.2885</v>
       </c>
       <c r="P21" t="n">
-        <v>0.1833</v>
+        <v>0.733</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.8326</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.0158</v>
+        <v>0.733</v>
       </c>
       <c r="S21" t="n">
-        <v>0.3217</v>
+        <v>-0.3305</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0392</v>
+        <v>-0.198</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3609</v>
+        <v>-0.1325</v>
       </c>
       <c r="V21" t="n">
-        <v>-2.2224</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.2224</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>D. ARIJA DE LA PENA</t>
+          <t>C. WHITSON</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.8235</v>
+        <v>-2.546</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.3754</v>
+        <v>-1.5032</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.4481</v>
+        <v>-1.0428</v>
       </c>
       <c r="G22" t="n">
-        <v>-4.3196</v>
+        <v>-0.7354000000000001</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.5246</v>
+        <v>0.6138</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.7951</v>
+        <v>-1.3492</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.1656</v>
+        <v>0.5609</v>
       </c>
       <c r="K22" t="n">
-        <v>0.1484</v>
+        <v>1.5573</v>
       </c>
       <c r="L22" t="n">
-        <v>-2.3141</v>
+        <v>-0.9964</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.154</v>
+        <v>-1.2962</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.673</v>
+        <v>-0.9434</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.481</v>
+        <v>-0.3528</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.4661</v>
+        <v>0.1833</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.9321</v>
+        <v>-1.8326</v>
       </c>
       <c r="R22" t="n">
-        <v>1.4661</v>
+        <v>2.0158</v>
       </c>
       <c r="S22" t="n">
-        <v>1.6848</v>
+        <v>0.2285</v>
       </c>
       <c r="T22" t="n">
-        <v>1.445</v>
+        <v>-0.2315</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2398</v>
+        <v>0.46</v>
       </c>
       <c r="V22" t="n">
-        <v>1.2774</v>
+        <v>-2.2224</v>
       </c>
       <c r="W22" t="n">
-        <v>1.2774</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-2.2224</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. ALBA GONZALEZ</t>
+          <t>D. ARIJA DE LA PENA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.8862</v>
+        <v>-3.0479</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.0606</v>
+        <v>-2.8561</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1743</v>
+        <v>-0.1917</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.4766</v>
+        <v>-4.3196</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.5856</v>
+        <v>-1.5246</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.891</v>
+        <v>-2.7951</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.8856</v>
+        <v>-2.1656</v>
       </c>
       <c r="K23" t="n">
-        <v>0.486</v>
+        <v>0.1484</v>
       </c>
       <c r="L23" t="n">
-        <v>-2.3717</v>
+        <v>-2.3141</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.591</v>
+        <v>-2.154</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.0716</v>
+        <v>-1.673</v>
       </c>
       <c r="O23" t="n">
-        <v>0.4807</v>
+        <v>-0.481</v>
       </c>
       <c r="P23" t="n">
-        <v>0.9163</v>
+        <v>-1.4661</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.9163</v>
+        <v>-2.9321</v>
       </c>
       <c r="R23" t="n">
-        <v>1.8326</v>
+        <v>1.4661</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.059</v>
+        <v>1.4604</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2586</v>
+        <v>0.9641999999999999</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1997</v>
+        <v>0.4962</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.267</v>
+        <v>1.2774</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.2774</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.267</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.8532</v>
+        <v>-3.4905</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.5702</v>
+        <v>-4.2817</v>
       </c>
       <c r="F24" t="n">
-        <v>0.717</v>
+        <v>0.7913</v>
       </c>
       <c r="G24" t="n">
         <v>-2.813</v>
@@ -2326,13 +2326,13 @@
         <v>0.9163</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.4459</v>
+        <v>-0.08309999999999999</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4955</v>
+        <v>-0.207</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0495</v>
+        <v>0.1239</v>
       </c>
       <c r="V24" t="n">
         <v>0.3219</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.3128</v>
+        <v>-4.6252</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.2876</v>
+        <v>-3.8068</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.0252</v>
+        <v>-0.8183</v>
       </c>
       <c r="G25" t="n">
         <v>-4.4103</v>
@@ -2404,13 +2404,13 @@
         <v>1.2828</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.803</v>
+        <v>-0.1154</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.5513</v>
+        <v>-0.07049999999999999</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.2517</v>
+        <v>-0.0449</v>
       </c>
       <c r="V25" t="n">
         <v>0.6335</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-18.1358</v>
+        <v>-16.854</v>
       </c>
       <c r="E26" t="n">
-        <v>-15.7295</v>
+        <v>-15.7292</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.4064</v>
+        <v>-1.1243</v>
       </c>
       <c r="G26" t="n">
         <v>-20.2152</v>
@@ -2452,13 +2452,13 @@
         <v>-11.7227</v>
       </c>
       <c r="I26" t="n">
-        <v>-8.4925</v>
+        <v>-8.492500000000001</v>
       </c>
       <c r="J26" t="n">
         <v>-4.9411</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.4572000000000002</v>
+        <v>-0.4572000000000004</v>
       </c>
       <c r="L26" t="n">
         <v>-4.4843</v>
@@ -2473,7 +2473,7 @@
         <v>-4.0082</v>
       </c>
       <c r="P26" t="n">
-        <v>0.0001000000000004331</v>
+        <v>9.999999999998899e-05</v>
       </c>
       <c r="Q26" t="n">
         <v>-14.6606</v>
@@ -2482,13 +2482,13 @@
         <v>14.6606</v>
       </c>
       <c r="S26" t="n">
-        <v>3.6576</v>
+        <v>4.939699999999999</v>
       </c>
       <c r="T26" t="n">
-        <v>1.6291</v>
+        <v>1.6292</v>
       </c>
       <c r="U26" t="n">
-        <v>2.0285</v>
+        <v>3.3106</v>
       </c>
       <c r="V26" t="n">
         <v>-1.5785</v>
